--- a/astro-site/public/dl/pizza-shop-business-plan/pizza-shop-financial-projections.xlsx
+++ b/astro-site/public/dl/pizza-shop-business-plan/pizza-shop-financial-projections.xlsx
@@ -751,7 +751,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Equivalent covers per day, year-1 average: about 47 dine-in (patio included from April through October) and about 15 from take-out and delivery, which are the orders (about 10 a day at about $52 excl. sales tax: 2 pizzas, a starter and a drink) divided by the average check. A Saturday runs about 110; a Tuesday, about 45 (Kit estimate). Compare it with the foot traffic on your street on a Friday night and a Tuesday at lunch</t>
+          <t>Equivalent covers per day, year-1 average: about 47 dine-in (patio included from April through October) and about 15 from take-out and delivery, which are the orders (about 10 a day at about $54 excl. sales tax: 2 pizzas, a starter and a drink) divided by the average check. A Saturday runs about 110; a Tuesday, about 45 (Kit estimate). Compare it with the foot traffic on your street on a Friday night and a Tuesday at lunch</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>365 days minus 52 closed Mondays, the main holidays (Thanksgiving, Christmas, New Year's Day, July 4) and a week in January for oven maintenance and vacation, rounded to 300. It is the SAME figure for the P&amp;L, break-even, scenarios and staffing hours</t>
+          <t>365 days minus 52 closed Mondays, the main holidays (Thanksgiving, Christmas, New Year's Day, July 4) and two weeks in January for oven maintenance and vacation, rounded to 300. It is the SAME figure for the P&amp;L, break-even, scenarios and staffing hours</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>General liability, liquor liability (beer &amp; wine), property coverage that names the open-flame oven, and workers' comp. Tell the carrier the oven is wood-fired: it changes the premium and the terms. Rates vary by state, so get at least two quotes</t>
+          <t>General liability, liquor liability (beer &amp; wine) and property coverage that names the open-flame oven (workers' comp is in the payroll tax rate above). Tell the carrier the oven is wood-fired: it changes the premium and the terms. Rates vary by state, so get at least two quotes</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="D12" s="29" t="inlineStr">
         <is>
-          <t>For about six pizzas at a time, UL 2162-listed. Forno Bravo posts $12,950 for its Modena120 (48 in); Marra Forni, Acunto and Ferrara publish no price. The range is $12,950-$25,000+ (Oct 2026); ask for a quote that includes installation. A gas or electric oven is a variant and does not qualify for VPN certification</t>
+          <t>For about six pizzas at a time, UL 2162-listed. Forno Bravo posts $12,950 for its Modena120 (48 in); Marra Forni, Acunto and Ferrara publish no price. The range is $12,950-$25,000+ (Oct 2026); ask for a quote that includes installation. A gas or electric oven is a variant: an electric oven never qualifies for VPN certification, and a gas oven only where wood burning is forbidden and documented</t>
         </is>
       </c>
       <c r="E12" s="32" t="inlineStr">
@@ -6196,7 +6196,7 @@
       <c r="I20" s="29" t="n"/>
       <c r="J20" s="29" t="inlineStr">
         <is>
-          <t>50 weeks: 52 minus about two weeks of vacation, holidays and average absences. There is no federal vacation requirement in the US: adjust it to your own policy</t>
+          <t>46 weeks: 52 minus about six weeks for vacation, holidays, the January closure and average absences. There is no federal vacation requirement in the US: adjust it to your own policy</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="B38" s="29" t="inlineStr">
         <is>
-          <t>1 quart (1 liter) of water per ~4 lb (1.8 kg) of flour, 50-55 g of salt, 3 g of fresh yeast</t>
+          <t>1.06 quarts (1 liter) of water per ~4 lb (1.8 kg) of flour, 50-55 g of salt, 3 g of fresh yeast</t>
         </is>
       </c>
       <c r="C38" s="29" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="D39" s="48" t="inlineStr">
         <is>
-          <t>Wood-fired dome oven; gas or electric is a variant and does not qualify for VPN</t>
+          <t>Wood-fired dome oven; gas only where wood is banned (documented); electric does not qualify for VPN</t>
         </is>
       </c>
       <c r="E39" s="29" t="n"/>
@@ -7031,7 +7031,7 @@
       </c>
       <c r="D40" s="48" t="inlineStr">
         <is>
-          <t>$2,500 certification + $300 inspection + $400 a year (USA/Canada); needs an open location and a wood-fired dome oven</t>
+          <t>$2,500 certification + $300 inspection + $400 a year (USA/Canada); needs an open location and a wood-fired dome oven (gas only where wood is banned)</t>
         </is>
       </c>
       <c r="E40" s="29" t="n"/>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="O20" s="29" t="inlineStr">
         <is>
-          <t>Cash only leaves when the quarter's result is positive. Months without a settlement are left blank, not zero. The cell turns RED when the payment takes more cash than is left that month. The model settles quarterly (April, July, October, January): if your state requires monthly filing, expect smaller payments every month instead</t>
+          <t>Cash only leaves when the quarter's result is positive. Months without a settlement are left blank, not zero. The cell turns RED when the payment takes more cash than is left that month. The model settles quarterly, in the month after each plan quarter (Months 4, 7 and 10: December, March and June with Month 1 in September; the fourth quarter is remitted in Month 13): if your state requires monthly filing, expect smaller payments every month instead</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/pizza-shop-business-plan/pizza-shop-financial-projections.xlsx
+++ b/astro-site/public/dl/pizza-shop-business-plan/pizza-shop-financial-projections.xlsx
@@ -826,7 +826,7 @@
         <v>38.88</v>
       </c>
       <c r="C9" t="str">
-        <f>IFERROR("Average check excl. sales tax plus the weighted sales tax of your sales lines ("&amp;TEXT(SUMPRODUCT('3-Year P&amp;L'!$E$10:$E$11,'3-Year P&amp;L'!$G$10:$G$11)*100,"0")&amp;"%), rounded. In the US, menu prices usually exclude sales tax and it is added at the register; the beverage share in column H of the beverage line of the P&amp;L only moves this average if your state taxes alcohol at another rate. In the UK, menu prices include VAT.","")</f>
+        <f>IFERROR("Average check excl. sales tax plus the weighted sales tax of your sales lines ("&amp;TEXT(SUMPRODUCT('3-Year P&amp;L'!$E$10:$E$11,'3-Year P&amp;L'!$G$10:$G$11)*100,"0")&amp;"%), rounded. In the US, menu prices usually exclude sales tax and it is added at the register; the beverage share in column H of the beverage line of the P&amp;L only moves this average if your state taxes alcohol at another rate. In the UK, "&amp;"menu prices include VAT.","")</f>
         <v>Average check excl. sales tax plus the weighted sales tax of your sales lines (8%), rounded. In the US, menu prices usually exclude sales tax and it is added at the register; the beverage share in column H of the beverage line of the P&amp;L only moves this average if your state taxes alcohol at another rate. In the UK, menu prices include VAT.</v>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
         <v>1.24</v>
       </c>
       <c r="C50" t="str">
-        <f>IFERROR("That is "&amp;TEXT(INT(ROUND(B50,1)),"0")&amp;"."&amp;TEXT(ROUND(MOD(ROUND(B50,1),1)*10,0),"0")&amp;" seat turns per day on the "&amp;TEXT($B$51,"0")&amp;" seats in the cell below. It includes the take-out and delivery covers, which do not take a table: the real turns of your dining room are lower (in the example, about three quarters of the covers eat in). Compare it with the ceiling on seat turns typed in ""Break-Even"".","")</f>
+        <f>IFERROR("That is "&amp;TEXT(INT(ROUND(B50,1)),"0")&amp;"."&amp;TEXT(ROUND(MOD(ROUND(B50,1),1)*10,0),"0")&amp;" seat turns per day on the "&amp;TEXT($B$51,"0")&amp;" seats in the cell below. It includes the take-out and delivery covers, which do not take a table: the real turns of your dining room are lower (in the example, about three quarters of the covers eat in). Compare it with the ceiling on "&amp;"seat turns typed in ""Break-Even"".","")</f>
         <v>That is 1.2 seat turns per day on the 50 seats in the cell below. It includes the take-out and delivery covers, which do not take a table: the real turns of your dining room are lower (in the example, about three quarters of the covers eat in). Compare it with the ceiling on seat turns typed in "Break-Even".</v>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
         <v>0.02809208006819846</v>
       </c>
       <c r="D27" s="29" t="str">
-        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$55,"0%")&amp;" of the BUILD-OUT items of this block (architect, MEP, hood &amp; flue drawings and permit fees; build-out, signage &amp; facade; flue/chimney, spark arrestor &amp; hearth pad; electrical service &amp; panel; plumbing, grease interceptor, HVAC &amp; makeup air), not of the whole block: the oven, the equipment and the other items are left out. No lender funds a build-out without a cushion: the percentage is in ""0. Assumptions""","")</f>
+        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$55,"0%")&amp;" of the BUILD-OUT items of this block (architect, MEP, hood &amp; flue drawings and permit fees; build-out, signage &amp; facade; flue/chimney, spark arrestor &amp; hearth pad; electrical service &amp; panel; plumbing, grease interceptor, HVAC &amp; makeup "&amp;"air), not of the whole block: the oven, the equipment and the other items are left out. No lender funds a build-out without a cushion: the percentage is in ""0. Assumptions""","")</f>
         <v>At 10% of the BUILD-OUT items of this block (architect, MEP, hood &amp; flue drawings and permit fees; build-out, signage &amp; facade; flue/chimney, spark arrestor &amp; hearth pad; electrical service &amp; panel; plumbing, grease interceptor, HVAC &amp; makeup air), not of the whole block: the oven, the equipment and the other items are left out. No lender funds a build-out without a cushion: the percentage is in "0. Assumptions"</v>
       </c>
       <c r="E27" s="29" t="inlineStr">
@@ -2746,7 +2746,7 @@
         <v>0.2132</v>
       </c>
       <c r="F13" s="29" t="str">
-        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$13,"0%")&amp;" of FOOD sales, not of total sales: beverages have their own line · 00 flour, cheeses (fior di latte, mozzarella di bufala), San Marzano tomatoes, cured meats and olive oil: check it against your distributor invoices and the Pizza Dough &amp; Food Cost Calculator","")</f>
+        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$13,"0%")&amp;" of FOOD sales, not of total sales: beverages have their own line · 00 flour, cheeses (fior di latte, mozzarella di bufala), San Marzano tomatoes, cured meats and olive oil: check it against your distributor invoices and the Pizza Dough &amp; "&amp;"Food Cost Calculator","")</f>
         <v>At 26% of FOOD sales, not of total sales: beverages have their own line · 00 flour, cheeses (fior di latte, mozzarella di bufala), San Marzano tomatoes, cured meats and olive oil: check it against your distributor invoices and the Pizza Dough &amp; Food Cost Calculator</v>
       </c>
       <c r="G13" s="74" t="n">

--- a/astro-site/public/dl/pizza-shop-business-plan/pizza-shop-financial-projections.xlsx
+++ b/astro-site/public/dl/pizza-shop-business-plan/pizza-shop-financial-projections.xlsx
@@ -1587,7 +1587,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>How far you can fall below plan before you start losing money</t>
+          <t>How far planned sales must sit above cash break-even (fixed costs and the loan payment). The drop you can absorb is somewhat smaller: with a 15% cushion, about 13% of plan</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="E24" s="29" t="inlineStr">
         <is>
-          <t>How far you can fall before you cannot pay the fixed costs and the loan payment. The required minimum is set in the "0. Assumptions" tab</t>
+          <t>How far planned sales sit above cash break-even. The drop you can absorb before you cannot pay the fixed costs and the loan payment is somewhat smaller: with a 25% cushion, 20%. The required minimum is set in the "0. Assumptions" tab</t>
         </is>
       </c>
       <c r="F24" s="29" t="n"/>

--- a/astro-site/public/dl/pizza-shop-business-plan/pizza-shop-financial-projections.xlsx
+++ b/astro-site/public/dl/pizza-shop-business-plan/pizza-shop-financial-projections.xlsx
@@ -826,7 +826,7 @@
         <v>38.88</v>
       </c>
       <c r="C9" t="str">
-        <f>IFERROR("Average check excl. sales tax plus the weighted sales tax of your sales lines ("&amp;TEXT(SUMPRODUCT('3-Year P&amp;L'!$E$10:$E$11,'3-Year P&amp;L'!$G$10:$G$11)*100,"0")&amp;"%), rounded. In the US, menu prices usually exclude sales tax and it is added at the register; the beverage share in column H of the beverage line of the P&amp;L only moves this average if your state taxes alcohol at another rate. In the UK, menu prices include VAT.","")</f>
+        <f>IFERROR("Average check excl. sales tax plus the weighted sales tax of your sales lines ("&amp;TEXT(SUMPRODUCT('3-Year P&amp;L'!$E$10:$E$11,'3-Year P&amp;L'!$G$10:$G$11)*100,"0")&amp;"%), rounded. In the US, menu prices usually exclude sales tax and it is added at the register; the beverage share in column H of the beverage line of the P&amp;L only moves this average if your state taxes alcohol at another rate. In the UK, "&amp;"menu prices include VAT.","")</f>
         <v>Average check excl. sales tax plus the weighted sales tax of your sales lines (8%), rounded. In the US, menu prices usually exclude sales tax and it is added at the register; the beverage share in column H of the beverage line of the P&amp;L only moves this average if your state taxes alcohol at another rate. In the UK, menu prices include VAT.</v>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
         <v>1.24</v>
       </c>
       <c r="C50" t="str">
-        <f>IFERROR("That is "&amp;TEXT(INT(ROUND(B50,1)),"0")&amp;"."&amp;TEXT(ROUND(MOD(ROUND(B50,1),1)*10,0),"0")&amp;" seat turns per day on the "&amp;TEXT($B$51,"0")&amp;" seats in the cell below. It includes the take-out and delivery covers, which do not take a table: the real turns of your dining room are lower (in the example, about three quarters of the covers eat in). Compare it with the ceiling on seat turns typed in ""Break-Even"".","")</f>
+        <f>IFERROR("That is "&amp;TEXT(INT(ROUND(B50,1)),"0")&amp;"."&amp;TEXT(ROUND(MOD(ROUND(B50,1),1)*10,0),"0")&amp;" seat turns per day on the "&amp;TEXT($B$51,"0")&amp;" seats in the cell below. It includes the take-out and delivery covers, which do not take a table: the real turns of your dining room are lower (in the example, about three quarters of the covers eat in). Compare it with the ceiling on "&amp;"seat turns typed in ""Break-Even"".","")</f>
         <v>That is 1.2 seat turns per day on the 50 seats in the cell below. It includes the take-out and delivery covers, which do not take a table: the real turns of your dining room are lower (in the example, about three quarters of the covers eat in). Compare it with the ceiling on seat turns typed in "Break-Even".</v>
       </c>
     </row>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>How far you can fall below plan before you start losing money</t>
+          <t>How far planned sales must sit above cash break-even (fixed costs and the loan payment). The drop you can absorb is somewhat smaller: with a 15% cushion, about 13% of plan</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
         <v>0.02809208006819846</v>
       </c>
       <c r="D27" s="29" t="str">
-        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$55,"0%")&amp;" of the BUILD-OUT items of this block (architect, MEP, hood &amp; flue drawings and permit fees; build-out, signage &amp; facade; flue/chimney, spark arrestor &amp; hearth pad; electrical service &amp; panel; plumbing, grease interceptor, HVAC &amp; makeup air), not of the whole block: the oven, the equipment and the other items are left out. No lender funds a build-out without a cushion: the percentage is in ""0. Assumptions""","")</f>
+        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$55,"0%")&amp;" of the BUILD-OUT items of this block (architect, MEP, hood &amp; flue drawings and permit fees; build-out, signage &amp; facade; flue/chimney, spark arrestor &amp; hearth pad; electrical service &amp; panel; plumbing, grease interceptor, HVAC &amp; makeup "&amp;"air), not of the whole block: the oven, the equipment and the other items are left out. No lender funds a build-out without a cushion: the percentage is in ""0. Assumptions""","")</f>
         <v>At 10% of the BUILD-OUT items of this block (architect, MEP, hood &amp; flue drawings and permit fees; build-out, signage &amp; facade; flue/chimney, spark arrestor &amp; hearth pad; electrical service &amp; panel; plumbing, grease interceptor, HVAC &amp; makeup air), not of the whole block: the oven, the equipment and the other items are left out. No lender funds a build-out without a cushion: the percentage is in "0. Assumptions"</v>
       </c>
       <c r="E27" s="29" t="inlineStr">
@@ -2746,7 +2746,7 @@
         <v>0.2132</v>
       </c>
       <c r="F13" s="29" t="str">
-        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$13,"0%")&amp;" of FOOD sales, not of total sales: beverages have their own line · 00 flour, cheeses (fior di latte, mozzarella di bufala), San Marzano tomatoes, cured meats and olive oil: check it against your distributor invoices and the Pizza Dough &amp; Food Cost Calculator","")</f>
+        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$13,"0%")&amp;" of FOOD sales, not of total sales: beverages have their own line · 00 flour, cheeses (fior di latte, mozzarella di bufala), San Marzano tomatoes, cured meats and olive oil: check it against your distributor invoices and the Pizza Dough &amp; "&amp;"Food Cost Calculator","")</f>
         <v>At 26% of FOOD sales, not of total sales: beverages have their own line · 00 flour, cheeses (fior di latte, mozzarella di bufala), San Marzano tomatoes, cured meats and olive oil: check it against your distributor invoices and the Pizza Dough &amp; Food Cost Calculator</v>
       </c>
       <c r="G13" s="74" t="n">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="E24" s="29" t="inlineStr">
         <is>
-          <t>How far you can fall before you cannot pay the fixed costs and the loan payment. The required minimum is set in the "0. Assumptions" tab</t>
+          <t>How far planned sales sit above cash break-even. The drop you can absorb before you cannot pay the fixed costs and the loan payment is somewhat smaller: with a 25% cushion, 20%. The required minimum is set in the "0. Assumptions" tab</t>
         </is>
       </c>
       <c r="F24" s="29" t="n"/>
